--- a/old/_260925_240621_0922_633.xlsx
+++ b/old/_260925_240621_0922_633.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85A60DF-34BF-486D-9AED-B615633B3DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0A0248-B8F1-4CA0-9BCE-CD91D99E475E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13610" yWindow="3420" windowWidth="15010" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15370" yWindow="4200" windowWidth="15010" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
     <t>Heilsversprechen</t>
   </si>
   <si>
-    <t>Aufgewühltheit ; aufwühlen 激起</t>
+    <t>aufgewühlen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
